--- a/AAII_Financials/Quarterly/LDSCY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/LDSCY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="92">
   <si>
     <t>LDSCY</t>
   </si>
@@ -656,77 +656,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -766,8 +773,14 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -807,8 +820,14 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -848,8 +867,14 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -865,8 +890,10 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,8 +933,14 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -947,8 +980,14 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -988,8 +1027,14 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,8 +1074,14 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1043,8 +1094,10 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1084,8 +1137,14 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1125,8 +1184,14 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1142,8 +1207,10 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1183,8 +1250,14 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1224,8 +1297,14 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1265,8 +1344,14 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1306,8 +1391,14 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1347,8 +1438,14 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1388,8 +1485,14 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1429,8 +1532,14 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1470,8 +1579,14 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1511,8 +1626,14 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1552,8 +1673,14 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1593,8 +1720,14 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1634,8 +1767,14 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1675,8 +1814,14 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1716,8 +1861,14 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1757,8 +1908,14 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1798,54 +1955,66 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1861,8 +2030,10 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1878,49 +2049,57 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>140000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>142700</v>
+      </c>
+      <c r="F41" s="3">
         <v>130400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>132900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>50400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>48800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>49600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>46800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>98500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>99400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>97600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>101700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>50700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>49400</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1960,254 +2139,296 @@
       <c r="O42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>549300</v>
+      </c>
+      <c r="E43" s="3">
+        <v>559900</v>
+      </c>
+      <c r="F43" s="3">
         <v>787700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>802800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>514200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>498300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>557600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>525700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>389000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>392300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>466200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>485400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>373600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>363900</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>73900</v>
+      </c>
+      <c r="E44" s="3">
+        <v>75400</v>
+      </c>
+      <c r="F44" s="3">
         <v>112900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>115100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>104700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>101400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>130000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>122600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>126300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>127400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>135500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>141100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>146000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>142200</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>114900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>117100</v>
+      </c>
+      <c r="F45" s="3">
         <v>371000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>378100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>255800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>247900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>16100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>15200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>111100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>112100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>26800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>28000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>86600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>84300</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>886000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>903100</v>
+      </c>
+      <c r="F46" s="3">
         <v>1419500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>1446800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>931500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>902600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>766700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>722900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>724900</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>731100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>728500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>758700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>656900</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>639800</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>796200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>811600</v>
+      </c>
+      <c r="F47" s="3">
         <v>763500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>778200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>723500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>701100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>719700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>678700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>678200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>684000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>639400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>665900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>665600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>648200</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>55500</v>
+      </c>
+      <c r="E48" s="3">
+        <v>56500</v>
+      </c>
+      <c r="F48" s="3">
         <v>55100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>56200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>54300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>52600</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="L48" s="3">
         <v>8800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>8900</v>
       </c>
-      <c r="L48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N48" s="3">
+      <c r="N48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="P48" s="3">
         <v>11100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>10800</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2215,40 +2436,46 @@
         <v>4000</v>
       </c>
       <c r="E49" s="3">
+        <v>4000</v>
+      </c>
+      <c r="F49" s="3">
+        <v>4000</v>
+      </c>
+      <c r="G49" s="3">
         <v>4100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3900</v>
-      </c>
-      <c r="G49" s="3">
-        <v>3800</v>
-      </c>
-      <c r="H49" s="3">
-        <v>4000</v>
       </c>
       <c r="I49" s="3">
         <v>3800</v>
       </c>
       <c r="J49" s="3">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="K49" s="3">
         <v>3800</v>
       </c>
       <c r="L49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="M49" s="3">
+        <v>3800</v>
+      </c>
+      <c r="N49" s="3">
         <v>4900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>5100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>7400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2288,8 +2515,14 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2329,49 +2562,61 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13496500</v>
+      </c>
+      <c r="E52" s="3">
+        <v>13756400</v>
+      </c>
+      <c r="F52" s="3">
         <v>13329000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>13585400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>13301200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>12888600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>12794500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>12064200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>12052600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>12155400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>11934700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>12428400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>12225400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>11906700</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2411,49 +2656,61 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15238200</v>
+      </c>
+      <c r="E54" s="3">
+        <v>15531600</v>
+      </c>
+      <c r="F54" s="3">
         <v>15571100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>15870700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>15014400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>14548600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>14284900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>13469500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>13468400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>13583300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>13307500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>13858000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>13566400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>13212800</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2469,8 +2726,10 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2486,254 +2745,292 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>48900</v>
+      </c>
+      <c r="E57" s="3">
+        <v>49800</v>
+      </c>
+      <c r="F57" s="3">
         <v>465100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>474000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>38800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>37600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>439600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>414500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>70700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>71300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>396600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>413000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>17300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>16900</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>985100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1004000</v>
+      </c>
+      <c r="F58" s="3">
         <v>1286400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1311100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>979300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>949000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>639300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>602800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1231400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1241900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1072700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1117000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>389700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>379500</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>388200</v>
+      </c>
+      <c r="E59" s="3">
+        <v>395700</v>
+      </c>
+      <c r="F59" s="3">
         <v>61800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>63000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>342400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>331800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>75100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>70800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>293000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>295500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>28100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>29200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>282100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>274700</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1542300</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1572000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1813300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1848200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1560700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1512300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1154000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1088100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1708800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1723400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1497300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1559300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>798000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>777200</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4979500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>5075400</v>
+      </c>
+      <c r="F61" s="3">
         <v>4996400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>5092500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4914800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4762300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>4314400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4068100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>3549000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>3579300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>3584100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>3732300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>3987300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>3883400</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>83200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>84800</v>
+      </c>
+      <c r="F62" s="3">
         <v>111600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>113700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>99500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>96400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>44200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>41700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>68200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>68800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>15900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>16500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>27200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>26500</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2773,8 +3070,14 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2814,8 +3117,14 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2855,49 +3164,61 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6605000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>6732200</v>
+      </c>
+      <c r="F66" s="3">
         <v>6921300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>7054400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>6575000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>6371000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>5512700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>5198000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>5326000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>5371400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>5097300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>5308100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>4817400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>4691800</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2913,8 +3234,10 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2954,8 +3277,14 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2995,8 +3324,14 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3036,8 +3371,14 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3077,49 +3418,61 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8065400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>8220700</v>
+      </c>
+      <c r="F72" s="3">
         <v>8090700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>8246300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>7861900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>7618000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>8128900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>7664900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>7552600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>7617100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>7634300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>7950100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>8157700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>7945100</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3159,8 +3512,14 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3200,8 +3559,14 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3241,49 +3606,61 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8631900</v>
+      </c>
+      <c r="E76" s="3">
+        <v>8798100</v>
+      </c>
+      <c r="F76" s="3">
         <v>8648500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>8814900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>8416100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>8155000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>8698600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>8202000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>8085600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>8154600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>8143200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>8480000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>8666100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>8440300</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3323,54 +3700,66 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3410,8 +3799,14 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3427,49 +3822,57 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>600</v>
+      </c>
+      <c r="E83" s="3">
+        <v>600</v>
+      </c>
+      <c r="F83" s="3">
         <v>1300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>1300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>-600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>-600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>1800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>1900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>-1200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>-1200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>2800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>3000</v>
       </c>
-      <c r="N83" s="3">
-        <v>0</v>
-      </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3509,8 +3912,14 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3550,8 +3959,14 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3591,8 +4006,14 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3632,8 +4053,14 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3673,49 +4100,61 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>122100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>124500</v>
+      </c>
+      <c r="F89" s="3">
         <v>19500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>19900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>96300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>93300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>71700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>67600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>108600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>109500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>101300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>105500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>102700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>100000</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3731,8 +4170,10 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3772,8 +4213,14 @@
       <c r="O91" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3813,8 +4260,14 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3854,49 +4307,61 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>79900</v>
+      </c>
+      <c r="E94" s="3">
+        <v>81400</v>
+      </c>
+      <c r="F94" s="3">
         <v>63800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>65100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-293300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-284200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>47600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>44900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-20200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-20400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-146400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-152500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>76700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>74700</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3912,49 +4377,57 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>92400</v>
+      </c>
+      <c r="E96" s="3">
+        <v>94200</v>
+      </c>
+      <c r="F96" s="3">
         <v>100800</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>102800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>95600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>92600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>105200</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>99200</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>87100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>87900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>93400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>97200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>82900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>80700</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3994,8 +4467,14 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4035,8 +4514,14 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4076,49 +4561,61 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-196100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-199900</v>
+      </c>
+      <c r="F100" s="3">
         <v>-44400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-45200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>198300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>192200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-146800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-138400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-89700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-90400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>68900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>71800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-183100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-178300</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4158,45 +4655,57 @@
       <c r="O101" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P101" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E102" s="3">
+        <v>6100</v>
+      </c>
+      <c r="F102" s="3">
         <v>39000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>39700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>1300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>1300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>-27500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-25900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-1300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-1300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>23800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>24800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-3700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-3600</v>
       </c>
     </row>
